--- a/resources/Comensales.xlsx
+++ b/resources/Comensales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BOOM\Documents\Programación 1\Corte 2\L26.2.p.c2.18.comensales\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1390F96D-0331-40EE-A04E-3E3810E94CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33213A3E-47FD-4305-AEBD-4C1531890276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,7 +185,7 @@
     <numFmt numFmtId="164" formatCode="[$$-540A]#,##0"/>
     <numFmt numFmtId="165" formatCode="[$$-409]#,##0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,6 +224,14 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -318,7 +326,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -390,6 +398,7 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -736,6 +745,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="1"/>
+      <c r="E1" s="31"/>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">

--- a/resources/Comensales.xlsx
+++ b/resources/Comensales.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BOOM\Documents\Programación 1\Corte 2\L26.2.p.c2.18.comensales\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BOOM\Documents\Programación 1\Corte 2\Proyectos Corte 2\L26.2.p.c2.18.comensales\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33213A3E-47FD-4305-AEBD-4C1531890276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2663D86C-7D56-46AC-B244-5428D9C153F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3210" yWindow="1035" windowWidth="15375" windowHeight="8625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
   <si>
     <t>COMENSALES</t>
   </si>
@@ -87,9 +87,6 @@
     <t>María</t>
   </si>
   <si>
-    <t>Álvarez</t>
-  </si>
-  <si>
     <t>Gustavo</t>
   </si>
   <si>
@@ -120,30 +117,9 @@
     <t>Peñaloza</t>
   </si>
   <si>
-    <t>Kevin</t>
-  </si>
-  <si>
-    <t>Latiegue</t>
-  </si>
-  <si>
-    <t>Gabriela</t>
-  </si>
-  <si>
-    <t>López</t>
-  </si>
-  <si>
-    <t>Luis</t>
-  </si>
-  <si>
     <t>García</t>
   </si>
   <si>
-    <t>Sebastián</t>
-  </si>
-  <si>
-    <t>Díaz</t>
-  </si>
-  <si>
     <t>M</t>
   </si>
   <si>
@@ -175,17 +151,21 @@
   </si>
   <si>
     <t>Porcentaje sin Descuento:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total de descuentos: </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="[$$-540A]#,##0"/>
+  <numFmts count="3">
     <numFmt numFmtId="165" formatCode="[$$-409]#,##0"/>
+    <numFmt numFmtId="167" formatCode="[$$-540A]#,##0.00"/>
+    <numFmt numFmtId="169" formatCode="[$$-409]#,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,12 +193,6 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -260,7 +234,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -292,15 +266,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -326,79 +291,77 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -450,8 +413,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BD2EA614-C4B1-4C3C-A2D8-073DF3B07B5D}" name="Table1" displayName="Table1" ref="A3:A15" totalsRowShown="0" headerRowDxfId="1" tableBorderDxfId="0">
-  <autoFilter ref="A3:A15" xr:uid="{BD2EA614-C4B1-4C3C-A2D8-073DF3B07B5D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BD2EA614-C4B1-4C3C-A2D8-073DF3B07B5D}" name="Table1" displayName="Table1" ref="A3:A11" totalsRowShown="0" headerRowDxfId="1" tableBorderDxfId="0">
+  <autoFilter ref="A3:A11" xr:uid="{BD2EA614-C4B1-4C3C-A2D8-073DF3B07B5D}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{7B1C9C2E-E839-4CCF-B9D1-D37F0EFED642}" name="nombre"/>
   </tableColumns>
@@ -722,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -745,7 +708,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="1"/>
-      <c r="E1" s="31"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
@@ -798,49 +761,49 @@
       <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="6">
         <v>111</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" s="15">
-        <v>18730</v>
-      </c>
-      <c r="F4" s="8">
-        <v>1</v>
-      </c>
-      <c r="G4" s="12">
-        <f t="shared" ref="G4:G15" ca="1" si="0">DATEDIF(E4, TODAY(), "y")</f>
-        <v>75</v>
-      </c>
-      <c r="H4" s="21">
+      <c r="D4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="11">
+        <v>37422</v>
+      </c>
+      <c r="F4" s="6">
+        <v>1</v>
+      </c>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G11" ca="1" si="0">DATEDIF(E4, TODAY(), "y")</f>
+        <v>23</v>
+      </c>
+      <c r="H4" s="24">
         <f ca="1">IF(OR(AND(G4&gt;50, D4="F"), AND(G4&gt;60, D4="M")), IF(F4=1, 5, IF(F4=2, 7, 10)) * 0.5, IF(F4=1, 5, IF(F4=2, 7, 10)))</f>
-        <v>2.5</v>
-      </c>
-      <c r="I4" s="6" t="b">
+        <v>5</v>
+      </c>
+      <c r="I4" s="5" t="b">
         <f ca="1">OR(AND(G4&gt;50, D4="F"), AND(G4&gt;60, D4="M"))</f>
-        <v>1</v>
-      </c>
-      <c r="J4" s="24">
+        <v>0</v>
+      </c>
+      <c r="J4" s="15">
         <f>COUNTIF($F$4:F4, 1) / COUNTA($B$4:B4)</f>
         <v>1</v>
       </c>
-      <c r="K4" s="24">
+      <c r="K4" s="15">
         <f>K5</f>
         <v>0</v>
       </c>
-      <c r="L4" s="24">
+      <c r="L4" s="15">
         <f>COUNTIF($F$4:F4, 3) / COUNTA($B$4:B4)</f>
         <v>0</v>
       </c>
-      <c r="M4" s="24">
+      <c r="M4" s="15">
         <f ca="1">COUNTIF($I$4:I4, TRUE) / COUNTA($B$4:B4)</f>
-        <v>1</v>
-      </c>
-      <c r="N4" s="24">
+        <v>0</v>
+      </c>
+      <c r="N4" s="15">
         <f ca="1">COUNTIF($I$4:I4, FALSE) / COUNTA($B$4:B4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -850,49 +813,49 @@
       <c r="B5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="7">
         <v>222</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="16">
-        <v>35875</v>
-      </c>
-      <c r="F5" s="9">
-        <v>3</v>
-      </c>
-      <c r="G5" s="11">
+      <c r="D5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="12">
+        <v>40019</v>
+      </c>
+      <c r="F5" s="7">
+        <v>1</v>
+      </c>
+      <c r="G5" s="9">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="H5" s="22">
-        <f t="shared" ref="H5:H15" ca="1" si="1">IF(OR(AND(G5&gt;50, D5="F"), AND(G5&gt;60, D5="M")), IF(F5=1, 5, IF(F5=2, 7, 10)) * 0.5, IF(F5=1, 5, IF(F5=2, 7, 10)))</f>
-        <v>10</v>
-      </c>
-      <c r="I5" s="20" t="b">
-        <f t="shared" ref="I5:I15" ca="1" si="2">OR(AND(G5&gt;50, D5="F"), AND(G5&gt;60, D5="M"))</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="25">
+        <v>16</v>
+      </c>
+      <c r="H5" s="23">
+        <f t="shared" ref="H5:H11" ca="1" si="1">IF(OR(AND(G5&gt;50, D5="F"), AND(G5&gt;60, D5="M")), IF(F5=1, 5, IF(F5=2, 7, 10)) * 0.5, IF(F5=1, 5, IF(F5=2, 7, 10)))</f>
+        <v>5</v>
+      </c>
+      <c r="I5" s="14" t="b">
+        <f t="shared" ref="I5:I11" ca="1" si="2">OR(AND(G5&gt;50, D5="F"), AND(G5&gt;60, D5="M"))</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="16">
         <f>COUNTIF($F$4:F5, 1) / COUNTA($B$4:B5)</f>
-        <v>0.5</v>
-      </c>
-      <c r="K5" s="25">
+        <v>1</v>
+      </c>
+      <c r="K5" s="16">
         <f>COUNTIF($F$4:F5, 2) / COUNTA($B$4:B5)</f>
         <v>0</v>
       </c>
-      <c r="L5" s="25">
+      <c r="L5" s="16">
         <f>COUNTIF($F$4:F5, 3) / COUNTA($B$4:B5)</f>
-        <v>0.5</v>
-      </c>
-      <c r="M5" s="25">
+        <v>0</v>
+      </c>
+      <c r="M5" s="16">
         <f ca="1">COUNTIF($I$4:I5, TRUE) / COUNTA($B$4:B5)</f>
-        <v>0.5</v>
-      </c>
-      <c r="N5" s="25">
+        <v>0</v>
+      </c>
+      <c r="N5" s="16">
         <f ca="1">COUNTIF($I$4:I5, FALSE) / COUNTA($B$4:B5)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -900,607 +863,408 @@
         <v>19</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="8">
+        <v>30</v>
+      </c>
+      <c r="C6" s="6">
         <v>333</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="15">
-        <v>37576</v>
-      </c>
-      <c r="F6" s="8">
+      <c r="D6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="11">
+        <v>24005</v>
+      </c>
+      <c r="F6" s="6">
+        <v>1</v>
+      </c>
+      <c r="G6" s="10">
+        <f t="shared" ca="1" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="H6" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="I6" s="5" t="b">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="15">
+        <f>COUNTIF($F$4:F6, 1) / COUNTA($B$4:B6)</f>
+        <v>1</v>
+      </c>
+      <c r="K6" s="15">
+        <f t="shared" ref="K6" si="3">K7</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="15">
+        <f>COUNTIF($F$4:F6, 3) / COUNTA($B$4:B6)</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="15">
+        <f ca="1">COUNTIF($I$4:I6, TRUE) / COUNTA($B$4:B6)</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="15">
+        <f ca="1">COUNTIF($I$4:I6, FALSE) / COUNTA($B$4:B6)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="7">
+        <v>444</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="12">
+        <v>27528</v>
+      </c>
+      <c r="F7" s="7">
+        <v>3</v>
+      </c>
+      <c r="G7" s="9">
+        <f t="shared" ca="1" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="H7" s="23">
+        <f t="shared" ca="1" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="I7" s="14" t="b">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="16">
+        <f>COUNTIF($F$4:F7, 1) / COUNTA($B$4:B7)</f>
+        <v>0.75</v>
+      </c>
+      <c r="K7" s="16">
+        <f>COUNTIF($F$4:F7, 2) / COUNTA($B$4:B7)</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="16">
+        <f>COUNTIF($F$4:F7, 3) / COUNTA($B$4:B7)</f>
+        <v>0.25</v>
+      </c>
+      <c r="M7" s="16">
+        <f ca="1">COUNTIF($I$4:I7, TRUE) / COUNTA($B$4:B7)</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="16">
+        <f ca="1">COUNTIF($I$4:I7, FALSE) / COUNTA($B$4:B7)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="6">
+        <v>555</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="11">
+        <v>38355</v>
+      </c>
+      <c r="F8" s="6">
+        <v>1</v>
+      </c>
+      <c r="G8" s="10">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="H8" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="I8" s="5" t="b">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="15">
+        <f>COUNTIF($F$4:F8, 1) / COUNTA($B$4:B8)</f>
+        <v>0.8</v>
+      </c>
+      <c r="K8" s="15">
+        <f t="shared" ref="K8" si="4">K9</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="L8" s="15">
+        <f>COUNTIF($F$4:F8, 3) / COUNTA($B$4:B8)</f>
+        <v>0.2</v>
+      </c>
+      <c r="M8" s="15">
+        <f ca="1">COUNTIF($I$4:I8, TRUE) / COUNTA($B$4:B8)</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="15">
+        <f ca="1">COUNTIF($I$4:I8, FALSE) / COUNTA($B$4:B8)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="7">
+        <v>666</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="12">
+        <v>34983</v>
+      </c>
+      <c r="F9" s="7">
         <v>2</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G9" s="9">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="H6" s="21">
+        <v>30</v>
+      </c>
+      <c r="H9" s="23">
         <f t="shared" ca="1" si="1"/>
         <v>7</v>
       </c>
-      <c r="I6" s="6" t="b">
+      <c r="I9" s="14" t="b">
         <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
-      <c r="J6" s="24">
-        <f>COUNTIF($F$4:F6, 1) / COUNTA($B$4:B6)</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="K6" s="24">
-        <f t="shared" ref="K6" si="3">K7</f>
-        <v>0.5</v>
-      </c>
-      <c r="L6" s="24">
-        <f>COUNTIF($F$4:F6, 3) / COUNTA($B$4:B6)</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="M6" s="24">
-        <f ca="1">COUNTIF($I$4:I6, TRUE) / COUNTA($B$4:B6)</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="N6" s="24">
-        <f ca="1">COUNTIF($I$4:I6, FALSE) / COUNTA($B$4:B6)</f>
+      <c r="J9" s="16">
+        <f>COUNTIF($F$4:F9, 1) / COUNTA($B$4:B9)</f>
         <v>0.66666666666666663</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="9">
-        <v>444</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="16">
-        <v>38943</v>
-      </c>
-      <c r="F7" s="9">
-        <v>2</v>
-      </c>
-      <c r="G7" s="11">
+      <c r="K9" s="16">
+        <f>COUNTIF($F$4:F9, 2) / COUNTA($B$4:B9)</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="L9" s="16">
+        <f>COUNTIF($F$4:F9, 3) / COUNTA($B$4:B9)</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="M9" s="16">
+        <f ca="1">COUNTIF($I$4:I9, TRUE) / COUNTA($B$4:B9)</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="16">
+        <f ca="1">COUNTIF($I$4:I9, FALSE) / COUNTA($B$4:B9)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="6">
+        <v>777</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="11">
+        <v>23596</v>
+      </c>
+      <c r="F10" s="6">
+        <v>3</v>
+      </c>
+      <c r="G10" s="10">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="H7" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="I7" s="20" t="b">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J7" s="25">
-        <f>COUNTIF($F$4:F7, 1) / COUNTA($B$4:B7)</f>
-        <v>0.25</v>
-      </c>
-      <c r="K7" s="25">
-        <f>COUNTIF($F$4:F7, 2) / COUNTA($B$4:B7)</f>
-        <v>0.5</v>
-      </c>
-      <c r="L7" s="25">
-        <f>COUNTIF($F$4:F7, 3) / COUNTA($B$4:B7)</f>
-        <v>0.25</v>
-      </c>
-      <c r="M7" s="25">
-        <f ca="1">COUNTIF($I$4:I7, TRUE) / COUNTA($B$4:B7)</f>
-        <v>0.25</v>
-      </c>
-      <c r="N7" s="25">
-        <f ca="1">COUNTIF($I$4:I7, FALSE) / COUNTA($B$4:B7)</f>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="8">
-        <v>555</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="15">
-        <v>38355</v>
-      </c>
-      <c r="F8" s="8">
-        <v>1</v>
-      </c>
-      <c r="G8" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="H8" s="21">
+        <v>61</v>
+      </c>
+      <c r="H10" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>5</v>
       </c>
-      <c r="I8" s="6" t="b">
+      <c r="I10" s="5" t="b">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J8" s="24">
-        <f>COUNTIF($F$4:F8, 1) / COUNTA($B$4:B8)</f>
-        <v>0.4</v>
-      </c>
-      <c r="K8" s="24">
-        <f t="shared" ref="K8" si="4">K9</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="L8" s="24">
-        <f>COUNTIF($F$4:F8, 3) / COUNTA($B$4:B8)</f>
-        <v>0.2</v>
-      </c>
-      <c r="M8" s="24">
-        <f ca="1">COUNTIF($I$4:I8, TRUE) / COUNTA($B$4:B8)</f>
-        <v>0.2</v>
-      </c>
-      <c r="N8" s="24">
-        <f ca="1">COUNTIF($I$4:I8, FALSE) / COUNTA($B$4:B8)</f>
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="9">
-        <v>666</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="16">
-        <v>15230</v>
-      </c>
-      <c r="F9" s="9">
-        <v>1</v>
-      </c>
-      <c r="G9" s="11">
+        <v>1</v>
+      </c>
+      <c r="J10" s="15">
+        <f>COUNTIF($F$4:F10, 1) / COUNTA($B$4:B10)</f>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="K10" s="15">
+        <f t="shared" ref="K10" si="5">K11</f>
+        <v>0.125</v>
+      </c>
+      <c r="L10" s="15">
+        <f>COUNTIF($F$4:F10, 3) / COUNTA($B$4:B10)</f>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="M10" s="15">
+        <f ca="1">COUNTIF($I$4:I10, TRUE) / COUNTA($B$4:B10)</f>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="N10" s="15">
+        <f ca="1">COUNTIF($I$4:I10, FALSE) / COUNTA($B$4:B10)</f>
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="27">
+        <v>888</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="28">
+        <v>24307</v>
+      </c>
+      <c r="F11" s="27">
+        <v>1</v>
+      </c>
+      <c r="G11" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>84</v>
-      </c>
-      <c r="H9" s="22">
+        <v>59</v>
+      </c>
+      <c r="H11" s="29">
         <f t="shared" ca="1" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="I9" s="20" t="b">
+      <c r="I11" s="13" t="b">
         <f t="shared" ca="1" si="2"/>
         <v>1</v>
       </c>
-      <c r="J9" s="25">
-        <f>COUNTIF($F$4:F9, 1) / COUNTA($B$4:B9)</f>
-        <v>0.5</v>
-      </c>
-      <c r="K9" s="25">
-        <f>COUNTIF($F$4:F9, 2) / COUNTA($B$4:B9)</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="L9" s="25">
-        <f>COUNTIF($F$4:F9, 3) / COUNTA($B$4:B9)</f>
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="M9" s="25">
-        <f ca="1">COUNTIF($I$4:I9, TRUE) / COUNTA($B$4:B9)</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="N9" s="25">
-        <f ca="1">COUNTIF($I$4:I9, FALSE) / COUNTA($B$4:B9)</f>
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="8">
-        <v>777</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="15">
-        <v>30735</v>
-      </c>
-      <c r="F10" s="8">
-        <v>1</v>
-      </c>
-      <c r="G10" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="H10" s="21">
-        <f t="shared" ca="1" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="I10" s="6" t="b">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="24">
-        <f>COUNTIF($F$4:F10, 1) / COUNTA($B$4:B10)</f>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="K10" s="24">
-        <f t="shared" ref="K10" si="5">K11</f>
-        <v>0.25</v>
-      </c>
-      <c r="L10" s="24">
-        <f>COUNTIF($F$4:F10, 3) / COUNTA($B$4:B10)</f>
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="M10" s="24">
-        <f ca="1">COUNTIF($I$4:I10, TRUE) / COUNTA($B$4:B10)</f>
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="N10" s="24">
-        <f ca="1">COUNTIF($I$4:I10, FALSE) / COUNTA($B$4:B10)</f>
-        <v>0.7142857142857143</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="9">
-        <v>888</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="16">
-        <v>37798</v>
-      </c>
-      <c r="F11" s="9">
-        <v>3</v>
-      </c>
-      <c r="G11" s="11">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="H11" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="I11" s="20" t="b">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="25">
+      <c r="J11" s="17">
         <f>COUNTIF($F$4:F11, 1) / COUNTA($B$4:B11)</f>
-        <v>0.5</v>
-      </c>
-      <c r="K11" s="25">
+        <v>0.625</v>
+      </c>
+      <c r="K11" s="17">
         <f>COUNTIF($F$4:F11, 2) / COUNTA($B$4:B11)</f>
-        <v>0.25</v>
-      </c>
-      <c r="L11" s="25">
+        <v>0.125</v>
+      </c>
+      <c r="L11" s="17">
         <f>COUNTIF($F$4:F11, 3) / COUNTA($B$4:B11)</f>
         <v>0.25</v>
       </c>
-      <c r="M11" s="25">
+      <c r="M11" s="17">
         <f ca="1">COUNTIF($I$4:I11, TRUE) / COUNTA($B$4:B11)</f>
         <v>0.25</v>
       </c>
-      <c r="N11" s="25">
+      <c r="N11" s="17">
         <f ca="1">COUNTIF($I$4:I11, FALSE) / COUNTA($B$4:B11)</f>
         <v>0.75</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="8">
-        <v>999</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="15">
-        <v>24721</v>
-      </c>
-      <c r="F12" s="8">
-        <v>2</v>
-      </c>
-      <c r="G12" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>58</v>
-      </c>
-      <c r="H12" s="21">
-        <f t="shared" ca="1" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="I12" s="6" t="b">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J12" s="24">
-        <f>COUNTIF($F$4:F12, 1) / COUNTA($B$4:B12)</f>
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="K12" s="24">
-        <f t="shared" ref="K12" si="6">K13</f>
-        <v>0.4</v>
-      </c>
-      <c r="L12" s="24">
-        <f>COUNTIF($F$4:F12, 3) / COUNTA($B$4:B12)</f>
-        <v>0.22222222222222221</v>
-      </c>
-      <c r="M12" s="24">
-        <f ca="1">COUNTIF($I$4:I12, TRUE) / COUNTA($B$4:B12)</f>
-        <v>0.22222222222222221</v>
-      </c>
-      <c r="N12" s="24">
-        <f ca="1">COUNTIF($I$4:I12, FALSE) / COUNTA($B$4:B12)</f>
-        <v>0.77777777777777779</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="11">
-        <v>1000</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="16">
-        <v>34436</v>
-      </c>
-      <c r="F13" s="11">
-        <v>2</v>
-      </c>
-      <c r="G13" s="11">
-        <f t="shared" ca="1" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="H13" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="I13" s="20" t="b">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J13" s="25">
-        <f>COUNTIF($F$4:F13, 1) / COUNTA($B$4:B13)</f>
-        <v>0.4</v>
-      </c>
-      <c r="K13" s="25">
-        <f>COUNTIF($F$4:F13, 2) / COUNTA($B$4:B13)</f>
-        <v>0.4</v>
-      </c>
-      <c r="L13" s="25">
-        <f>COUNTIF($F$4:F13, 3) / COUNTA($B$4:B13)</f>
-        <v>0.2</v>
-      </c>
-      <c r="M13" s="25">
-        <f ca="1">COUNTIF($I$4:I13, TRUE) / COUNTA($B$4:B13)</f>
-        <v>0.2</v>
-      </c>
-      <c r="N13" s="25">
-        <f ca="1">COUNTIF($I$4:I13, FALSE) / COUNTA($B$4:B13)</f>
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="13">
-        <v>1111</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="17">
-        <v>26723</v>
-      </c>
-      <c r="F14" s="8">
-        <v>1</v>
-      </c>
-      <c r="G14" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>53</v>
-      </c>
-      <c r="H14" s="21">
-        <f t="shared" ca="1" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="I14" s="6" t="b">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="24">
-        <f>COUNTIF($F$4:F14, 1) / COUNTA($B$4:B14)</f>
-        <v>0.45454545454545453</v>
-      </c>
-      <c r="K14" s="24">
-        <f t="shared" ref="K14" si="7">K15</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="L14" s="24">
-        <f>COUNTIF($F$4:F14, 3) / COUNTA($B$4:B14)</f>
-        <v>0.18181818181818182</v>
-      </c>
-      <c r="M14" s="24">
-        <f ca="1">COUNTIF($I$4:I14, TRUE) / COUNTA($B$4:B14)</f>
-        <v>0.18181818181818182</v>
-      </c>
-      <c r="N14" s="24">
-        <f ca="1">COUNTIF($I$4:I14, FALSE) / COUNTA($B$4:B14)</f>
-        <v>0.81818181818181823</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="10">
-        <v>2222</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="18">
-        <v>37050</v>
-      </c>
-      <c r="F15" s="10">
-        <v>3</v>
-      </c>
-      <c r="G15" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="H15" s="23">
-        <f t="shared" ca="1" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="I15" s="19" t="b">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="26">
-        <f>COUNTIF($F$4:F15, 1) / COUNTA($B$4:B15)</f>
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K15" s="26">
-        <f>COUNTIF($F$4:F15, 2) / COUNTA($B$4:B15)</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="L15" s="26">
-        <f>COUNTIF($F$4:F15, 3) / COUNTA($B$4:B15)</f>
-        <v>0.25</v>
-      </c>
-      <c r="M15" s="26">
-        <f ca="1">COUNTIF($I$4:I15, TRUE) / COUNTA($B$4:B15)</f>
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="N15" s="26">
-        <f ca="1">COUNTIF($I$4:I15, FALSE) / COUNTA($B$4:B15)</f>
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
     <row r="17" spans="5:9">
       <c r="E17" t="s">
-        <v>41</v>
-      </c>
-      <c r="I17" s="29">
-        <f ca="1">SUM(H4:H15)</f>
-        <v>78</v>
+        <v>33</v>
+      </c>
+      <c r="I17" s="20">
+        <f ca="1">SUM(H4:H11)</f>
+        <v>44.5</v>
       </c>
     </row>
     <row r="18" spans="5:9">
       <c r="E18" t="s">
-        <v>42</v>
-      </c>
-      <c r="I18" s="30">
-        <f ca="1">SUMIF(F4:F15, 1, H4:H15)</f>
-        <v>20</v>
+        <v>34</v>
+      </c>
+      <c r="I18" s="21">
+        <f ca="1">SUMIF(F4:F11, 1, H4:H11)</f>
+        <v>22.5</v>
       </c>
     </row>
     <row r="19" spans="5:9">
       <c r="E19" t="s">
-        <v>43</v>
-      </c>
-      <c r="I19" s="30">
-        <f ca="1">SUMIF(F4:F15, 2, H4:H15)</f>
-        <v>28</v>
+        <v>35</v>
+      </c>
+      <c r="I19" s="21">
+        <f ca="1">SUMIF(F4:F11, 2, H4:H11)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="5:9">
       <c r="E20" t="s">
-        <v>44</v>
-      </c>
-      <c r="I20" s="30">
-        <f ca="1">SUMIF(F4:F15, 3, H4:H15)</f>
-        <v>30</v>
+        <v>36</v>
+      </c>
+      <c r="I20" s="21">
+        <f ca="1">SUMIF(F4:F11, 3, H4:H11)</f>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="5:9">
       <c r="E21" t="s">
-        <v>45</v>
-      </c>
-      <c r="I21" s="27">
-        <f>COUNTIF(F4:F15, 1) / COUNTA(B4:B15)</f>
-        <v>0.41666666666666669</v>
+        <v>37</v>
+      </c>
+      <c r="I21" s="18">
+        <f>COUNTIF(F4:F11, 1) / COUNTA(B4:B11)</f>
+        <v>0.625</v>
       </c>
     </row>
     <row r="22" spans="5:9">
       <c r="E22" t="s">
-        <v>46</v>
-      </c>
-      <c r="I22" s="27">
-        <f>COUNTIF(F4:F15, 2) / COUNTA(B4:B15)</f>
-        <v>0.33333333333333331</v>
+        <v>38</v>
+      </c>
+      <c r="I22" s="18">
+        <f>COUNTIF(F4:F11, 2) / COUNTA(B4:B11)</f>
+        <v>0.125</v>
       </c>
     </row>
     <row r="23" spans="5:9">
       <c r="E23" t="s">
-        <v>47</v>
-      </c>
-      <c r="I23" s="28">
-        <f>COUNTIF(F4:F15, 3) / COUNTA(B4:B15)</f>
+        <v>39</v>
+      </c>
+      <c r="I23" s="19">
+        <f>COUNTIF(F4:F11, 3) / COUNTA(B4:B11)</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="24" spans="5:9">
       <c r="E24" t="s">
-        <v>48</v>
-      </c>
-      <c r="I24" s="28">
-        <f ca="1">COUNTIF(I4:I15, TRUE) / COUNTA(B4:B15)</f>
-        <v>0.16666666666666666</v>
+        <v>40</v>
+      </c>
+      <c r="I24" s="19">
+        <f ca="1">COUNTIF(I4:I11, TRUE) / COUNTA(B4:B11)</f>
+        <v>0.25</v>
       </c>
     </row>
     <row r="25" spans="5:9">
       <c r="E25" t="s">
-        <v>49</v>
-      </c>
-      <c r="I25" s="28">
-        <f ca="1">COUNTIF(I4:I15, FALSE) / COUNTA(B4:B15)</f>
-        <v>0.83333333333333337</v>
+        <v>41</v>
+      </c>
+      <c r="I25" s="19">
+        <f ca="1">COUNTIF(I4:I11, FALSE) / COUNTA(B4:B11)</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="26" spans="5:9">
+      <c r="E26" t="s">
+        <v>42</v>
+      </c>
+      <c r="I26" s="25">
+        <f ca="1">SUMIF(I4:I11, TRUE, H4:H11)</f>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="J14 J5:J13 L5:L13 L14" formulaRange="1"/>
-    <ignoredError sqref="K5:K14" formula="1" formulaRange="1"/>
+    <ignoredError sqref="J5:J11 L5:L11" formulaRange="1"/>
+    <ignoredError sqref="K5:K11" formula="1" formulaRange="1"/>
   </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
